--- a/artfynd/A 23750-2024 artfynd.xlsx
+++ b/artfynd/A 23750-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119724809</v>
+        <v>119724837</v>
       </c>
       <c r="B2" t="n">
         <v>90562</v>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>797420</v>
+        <v>797408</v>
       </c>
       <c r="R2" t="n">
-        <v>7162035</v>
+        <v>7162034</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119724870</v>
+        <v>119724809</v>
       </c>
       <c r="B3" t="n">
-        <v>82305</v>
+        <v>90562</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>797409</v>
+        <v>797420</v>
       </c>
       <c r="R3" t="n">
-        <v>7162041</v>
+        <v>7162035</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119724837</v>
+        <v>119724853</v>
       </c>
       <c r="B4" t="n">
-        <v>90562</v>
+        <v>82305</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,21 +911,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>797408</v>
+        <v>797398</v>
       </c>
       <c r="R4" t="n">
-        <v>7162034</v>
+        <v>7162039</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1115,7 +1115,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119724853</v>
+        <v>119724870</v>
       </c>
       <c r="B6" t="n">
         <v>82305</v>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>797398</v>
+        <v>797409</v>
       </c>
       <c r="R6" t="n">
-        <v>7162039</v>
+        <v>7162041</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 23750-2024 artfynd.xlsx
+++ b/artfynd/A 23750-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119724837</v>
+        <v>119724879</v>
       </c>
       <c r="B2" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>797408</v>
+        <v>797410</v>
       </c>
       <c r="R2" t="n">
-        <v>7162034</v>
+        <v>7162042</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119724809</v>
+        <v>119724870</v>
       </c>
       <c r="B3" t="n">
-        <v>90562</v>
+        <v>82305</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>797420</v>
+        <v>797409</v>
       </c>
       <c r="R3" t="n">
-        <v>7162035</v>
+        <v>7162041</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119724879</v>
+        <v>119724809</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,27 +1021,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>797410</v>
+        <v>797420</v>
       </c>
       <c r="R5" t="n">
-        <v>7162042</v>
+        <v>7162035</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119724870</v>
+        <v>119724837</v>
       </c>
       <c r="B6" t="n">
-        <v>82305</v>
+        <v>90562</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,21 +1131,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>797409</v>
+        <v>797408</v>
       </c>
       <c r="R6" t="n">
-        <v>7162041</v>
+        <v>7162034</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 23750-2024 artfynd.xlsx
+++ b/artfynd/A 23750-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119724879</v>
+        <v>119724809</v>
       </c>
       <c r="B2" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>797410</v>
+        <v>797420</v>
       </c>
       <c r="R2" t="n">
-        <v>7162042</v>
+        <v>7162035</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119724870</v>
+        <v>119724879</v>
       </c>
       <c r="B3" t="n">
-        <v>82305</v>
+        <v>78526</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,27 +801,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>797409</v>
+        <v>797410</v>
       </c>
       <c r="R3" t="n">
-        <v>7162041</v>
+        <v>7162042</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,7 +895,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119724853</v>
+        <v>119724870</v>
       </c>
       <c r="B4" t="n">
         <v>82305</v>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>797398</v>
+        <v>797409</v>
       </c>
       <c r="R4" t="n">
-        <v>7162039</v>
+        <v>7162041</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,7 +1005,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119724809</v>
+        <v>119724837</v>
       </c>
       <c r="B5" t="n">
         <v>90562</v>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>797420</v>
+        <v>797408</v>
       </c>
       <c r="R5" t="n">
-        <v>7162035</v>
+        <v>7162034</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119724837</v>
+        <v>119724853</v>
       </c>
       <c r="B6" t="n">
-        <v>90562</v>
+        <v>82305</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,21 +1131,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>797408</v>
+        <v>797398</v>
       </c>
       <c r="R6" t="n">
-        <v>7162034</v>
+        <v>7162039</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 23750-2024 artfynd.xlsx
+++ b/artfynd/A 23750-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119724809</v>
+        <v>119724837</v>
       </c>
       <c r="B2" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>797420</v>
+        <v>797408</v>
       </c>
       <c r="R2" t="n">
-        <v>7162035</v>
+        <v>7162034</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119724879</v>
+        <v>119724870</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>82321</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,27 +801,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>797410</v>
+        <v>797409</v>
       </c>
       <c r="R3" t="n">
-        <v>7162042</v>
+        <v>7162041</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119724870</v>
+        <v>119724879</v>
       </c>
       <c r="B4" t="n">
-        <v>82305</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,27 +911,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>797409</v>
+        <v>797410</v>
       </c>
       <c r="R4" t="n">
-        <v>7162041</v>
+        <v>7162042</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119724837</v>
+        <v>119724809</v>
       </c>
       <c r="B5" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>797408</v>
+        <v>797420</v>
       </c>
       <c r="R5" t="n">
-        <v>7162034</v>
+        <v>7162035</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,7 +1118,7 @@
         <v>119724853</v>
       </c>
       <c r="B6" t="n">
-        <v>82305</v>
+        <v>82321</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
